--- a/docs/research/provinces/SportsHub-Ontario.xlsx
+++ b/docs/research/provinces/SportsHub-Ontario.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Leagues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Club-League Map" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Club Sizes (ON elite)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$264</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Club Sizes (ON elite)'!$A$1:$D$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -562,7 +564,6 @@
           <t>1045 Upper Paradise Rd, Hamilton, ON L9B 2V2</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>ancastermagic@gmail.com</t>
@@ -573,7 +574,6 @@
           <t>https://www.ancastermagic.ca/</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -584,15 +584,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -630,8 +626,6 @@
           <t>info@bramptoncityprep.com</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Prep program</t>
@@ -642,15 +636,11 @@
           <t>NPA, OSBA; NJC+NPH-D1+NSC+OSBA</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -708,9 +698,6 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -778,15 +765,11 @@
           <t>NPH Showcase; Coalition</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -809,11 +792,6 @@
           <t>Brampton</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Rep, Elite</t>
@@ -824,15 +802,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -890,9 +864,6 @@
           <t>OBA, AAU</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -925,8 +896,6 @@
           <t>Brampton/Vaughan/Markham/Mississauga/Niagara</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>via website</t>
@@ -937,22 +906,16 @@
           <t>https://www.riseupleague.com/</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Beginner-friendly recreational</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1010,15 +973,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1056,7 +1015,6 @@
           <t>TRChockey@therisecentre.com</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Jim Wilson, Chief Executive Officer</t>
@@ -1072,9 +1030,6 @@
           <t>OSBA</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -1127,7 +1082,6 @@
           <t>https://www.burlingtonbasketball.ca/</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Rep, House league, Ages 5-18</t>
@@ -1138,9 +1092,6 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -1173,11 +1124,6 @@
           <t>Burlington</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -1188,15 +1134,11 @@
           <t>NJC</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1254,9 +1196,6 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -1309,7 +1248,6 @@
           <t>https://www.caledoncougars.ca/</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Prep program</t>
@@ -1320,9 +1258,6 @@
           <t>OSBA</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -1355,8 +1290,6 @@
           <t>Chatham</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>via website</t>
@@ -1367,7 +1300,6 @@
           <t>http://www.chathamkentwildcats.com/</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Rep, House league</t>
@@ -1378,15 +1310,11 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1409,11 +1337,6 @@
           <t>Dundas</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -1424,15 +1347,11 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1475,7 +1394,6 @@
           <t>https://www.durhamcitybasketball.ca/</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Rep (Durham City Bulldogs)</t>
@@ -1486,15 +1404,11 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1537,7 +1451,6 @@
           <t>www.gatorsbasketballacademy.com</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -1548,15 +1461,11 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1579,7 +1488,6 @@
           <t>Durham Region</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>905-836-6195</t>
@@ -1610,15 +1518,11 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1641,7 +1545,6 @@
           <t>Durham Region (Pickering/Ajax/Oshawa/Whitby)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>647-533-8635</t>
@@ -1657,7 +1560,6 @@
           <t>https://www.durhambluesbasketball.com/</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>House league, Rep ages U10-U19</t>
@@ -1668,15 +1570,11 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1699,15 +1597,11 @@
           <t>East Gwillimbury</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>gbunited.ca</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -1718,15 +1612,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1784,15 +1674,11 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1825,7 +1711,6 @@
           <t>416-393-5540</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>https://www.tcdsb.org/schools/fatherjohnredmond/</t>
@@ -1846,9 +1731,6 @@
           <t>OSBA</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -1886,14 +1768,11 @@
           <t>Centre Wellington District High School, Fergus, ON</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>https://cwceltics.ca/</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -1904,15 +1783,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1970,9 +1845,6 @@
           <t>NPA, OSBA</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -2040,15 +1912,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2071,8 +1939,6 @@
           <t>GTA-wide</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>via website</t>
@@ -2083,7 +1949,6 @@
           <t>https://www.girlsplaytoo.ca/aau</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>AAU girls program</t>
@@ -2094,15 +1959,11 @@
           <t>AAU</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2130,7 +1991,6 @@
           <t>145 rue de l'Atmosphère, Gatineau, QC, J9A 3G3; 850 boulevard de la Gappe, Gatineau, QC, J8T 7T7</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>info@basketballgatineau.com</t>
@@ -2156,9 +2016,6 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -2211,7 +2068,6 @@
           <t>guelphbasketball.com</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -2222,15 +2078,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2288,15 +2140,11 @@
           <t>NSC</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2319,11 +2167,6 @@
           <t>Hamilton</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Prep, Multi-division</t>
@@ -2334,15 +2177,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2385,7 +2224,6 @@
           <t>https://www.lincolnprep.ca/</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Prep program</t>
@@ -2396,9 +2234,6 @@
           <t>NPA, OSBA, NJC; NPH-D1+OSBA</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -2436,7 +2271,6 @@
           <t>145 Kirkpatrick St, Kingston, ON K7K 2P4</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>info@kingstonimpact.ca</t>
@@ -2462,15 +2296,11 @@
           <t>NPH Showcase; JUEL</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2528,9 +2358,6 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -2573,7 +2400,6 @@
           <t>519-621-4050</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>https://stbenedict.wcdsb.ca/</t>
@@ -2594,15 +2420,11 @@
           <t>NSC</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2660,15 +2482,11 @@
           <t>NPH Showcase; Coalition</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2696,10 +2514,6 @@
           <t>Waterloo, Ontario</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -2710,15 +2524,11 @@
           <t>NPA, NPH Showcase</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2741,9 +2551,6 @@
           <t>London</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>https://www.londonbasketballacademy.ca/</t>
@@ -2764,15 +2571,11 @@
           <t>NSC, NJC</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2795,8 +2598,6 @@
           <t>London</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>via website</t>
@@ -2807,22 +2608,16 @@
           <t>https://www.londoncyobasketball.com/</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>House league, Rep</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2850,7 +2645,6 @@
           <t>220 Sunnyside Dr</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>via website</t>
@@ -2871,10 +2665,6 @@
           <t>Youth programs</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -2907,9 +2697,6 @@
           <t>London</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>swfacademy.com</t>
@@ -2930,9 +2717,6 @@
           <t>OSBA; NPH-D1+OSBA</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -3000,15 +2784,11 @@
           <t>OSBA</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3066,9 +2846,6 @@
           <t>OSBA, NSC, NJC; NPH-D1+OSBA</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -3136,9 +2913,6 @@
           <t>OBA, AAU; NSC</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -3171,7 +2945,6 @@
           <t>Mississauga</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>416-346-6244</t>
@@ -3187,7 +2960,6 @@
           <t>ckatt.com</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -3198,9 +2970,6 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -3253,7 +3022,6 @@
           <t>http://www.mmba.on.ca/</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>House league, Rep</t>
@@ -3264,15 +3032,11 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3330,15 +3094,11 @@
           <t>OBA, AAU</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3396,15 +3156,11 @@
           <t>NSC</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3462,15 +3218,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3528,9 +3280,6 @@
           <t>OBA; OBL</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -3598,9 +3347,6 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -3633,7 +3379,6 @@
           <t>Niagara</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>(905) 714-5520</t>
@@ -3649,7 +3394,6 @@
           <t>https://blueprintbasketball.ca/</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -3660,9 +3404,6 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -3700,7 +3441,6 @@
           <t>6009 Valley Way, Niagara Falls, ON L2E 1X9</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>info@niagaraprepbasketball.com</t>
@@ -3726,15 +3466,11 @@
           <t>OSBA</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3792,15 +3528,11 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3858,9 +3590,6 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -3928,15 +3657,11 @@
           <t>OSBA</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3989,10 +3714,6 @@
           <t>Camps, Skill development, Rep</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -4060,15 +3781,11 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4091,11 +3808,6 @@
           <t>Oakville</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Prep program</t>
@@ -4106,15 +3818,11 @@
           <t>NJC</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4137,11 +3845,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -4152,15 +3855,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4188,7 +3887,6 @@
           <t>135 King St W</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>info@4qt.ca</t>
@@ -4199,7 +3897,6 @@
           <t>4qt.ca</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -4210,15 +3907,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4241,11 +3934,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>Prep</t>
@@ -4256,15 +3944,11 @@
           <t>NPH Showcase; NJC+NPH-SL</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4287,11 +3971,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Elite</t>
@@ -4302,15 +3981,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4333,11 +4008,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Girls Rep</t>
@@ -4348,15 +4018,11 @@
           <t>NPH Showcase Girls</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4379,11 +4045,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -4394,15 +4055,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4425,8 +4082,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>register@ball905.com</t>
@@ -4437,7 +4092,6 @@
           <t>ball905rep.com</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -4448,15 +4102,11 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4489,7 +4139,6 @@
           <t>905-389-7834</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>https://blessedsacramentbasketball.ca/</t>
@@ -4510,9 +4159,6 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -4545,11 +4191,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Prep</t>
@@ -4560,15 +4201,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4611,7 +4248,6 @@
           <t>https://www.cbelite.ca/</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -4622,15 +4258,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4653,9 +4285,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>cadouganelite.com</t>
@@ -4676,15 +4305,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4707,11 +4332,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -4722,15 +4342,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4768,8 +4384,6 @@
           <t>northernkingsacademy@gmail.com</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>Rep, Prep</t>
@@ -4780,15 +4394,11 @@
           <t>NPH Showcase; NJC+NPH-SL</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4811,8 +4421,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>cmeelitebasketball23@gmail.com</t>
@@ -4823,7 +4431,6 @@
           <t>cmeelitebasketball.com</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>Elite</t>
@@ -4834,15 +4441,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4865,7 +4468,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>519-991-2631</t>
@@ -4881,7 +4483,6 @@
           <t>https://www.corecityhoops.com/</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -4892,15 +4493,11 @@
           <t>NSC</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4923,11 +4520,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -4938,15 +4530,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4969,11 +4557,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>Academy</t>
@@ -4984,15 +4567,11 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5015,11 +4594,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -5030,15 +4604,11 @@
           <t>NJC</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5061,11 +4631,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>Girls Rep</t>
@@ -5076,15 +4641,11 @@
           <t>NPH Showcase Girls</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5107,11 +4668,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>Girls Rep</t>
@@ -5122,15 +4678,11 @@
           <t>NPH Showcase Girls; NPH-D1+NPH-SL</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5188,15 +4740,11 @@
           <t>NPH Showcase; NJC+NPH-SL</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5219,9 +4767,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>https://ecohoops.ca/</t>
@@ -5242,15 +4787,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5273,11 +4814,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>Prep, Varsity</t>
@@ -5288,15 +4824,11 @@
           <t>NPA, NPH Showcase</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5339,7 +4871,6 @@
           <t>https://elevationathletics.ca</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -5350,15 +4881,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5381,11 +4908,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>Academy</t>
@@ -5396,15 +4918,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5427,15 +4945,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>https://escadron.com</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -5446,15 +4960,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5487,7 +4997,6 @@
           <t>(647) 879-8344</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>eurostepbasketball.com</t>
@@ -5508,9 +5017,6 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -5548,7 +5054,6 @@
           <t>Turner Fenton Secondary School, 7935 Kennedy Rd S, Brampton, ON L6W 0A2</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>info@excelhoops.com</t>
@@ -5559,7 +5064,6 @@
           <t>https://www.excelhoops.com/</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -5570,15 +5074,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5601,10 +5101,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Jermaine Lyle</t>
@@ -5620,15 +5116,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5651,10 +5143,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Jermaine Lyle | Founder; Sheldon McIntosh | Coach</t>
@@ -5670,9 +5158,6 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -5705,15 +5190,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>https://fundamentalsfirstba.com/</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -5724,9 +5205,6 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -5759,11 +5237,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -5774,15 +5247,11 @@
           <t>NPH Showcase; NJC+NPH-SL</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5805,15 +5274,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>glorycanball.com</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -5824,15 +5289,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5855,8 +5316,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>info@lasalleguardiansbasketball.com</t>
@@ -5867,7 +5326,6 @@
           <t>https://lasalleguardiansbasketball.com/</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -5878,15 +5336,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5914,7 +5368,6 @@
           <t>725 Bathurst St, Toronto, ON M5S 2R5</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>h5academy@h5f.ca</t>
@@ -5940,15 +5393,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5971,8 +5420,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>HQelitecanada1@gmail.com</t>
@@ -5998,15 +5445,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6064,15 +5507,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6095,11 +5534,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>Elite</t>
@@ -6110,15 +5544,11 @@
           <t>NJC</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6176,15 +5606,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6207,7 +5633,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>(647) 296-3646</t>
@@ -6218,7 +5643,6 @@
           <t>infok9elite@gmail.com</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Terry House Jr., Program Director</t>
@@ -6234,9 +5658,6 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -6269,11 +5690,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>Elite</t>
@@ -6284,15 +5700,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6335,7 +5747,6 @@
           <t>https://kingheightsacademy.com/</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>Prep program</t>
@@ -6346,9 +5757,6 @@
           <t>NPA, OSBA; NPH-SL+OSBA</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -6381,11 +5789,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>Academy</t>
@@ -6396,15 +5799,11 @@
           <t>NJC</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6427,11 +5826,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -6442,15 +5836,11 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6508,15 +5898,11 @@
           <t>NPH Showcase; NPH-SL+NSC</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6549,7 +5935,6 @@
           <t>647-945-6945</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>https://mumbabasketball.ca/</t>
@@ -6570,15 +5955,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6601,15 +5982,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>mcelite.clubcentral.com</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>Rep, Multi-division (Black &amp; White)</t>
@@ -6620,9 +5997,6 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -6690,15 +6064,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6721,11 +6091,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -6736,15 +6101,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6767,11 +6128,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -6782,15 +6138,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6813,14 +6165,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>norwoodstarsbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Jenieve Grant | Director</t>
@@ -6836,15 +6185,11 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6867,11 +6212,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -6882,15 +6222,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6913,7 +6249,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>613-316-5668</t>
@@ -6944,15 +6279,11 @@
           <t>NSC, NPH Showcase</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6975,7 +6306,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>(647) 637-3859</t>
@@ -7006,15 +6336,11 @@
           <t>NPH Showcase; NPH-D1+NPH-SL</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7042,7 +6368,6 @@
           <t>952 Century Dr</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>polarisprepacademy@gmail.com</t>
@@ -7068,9 +6393,6 @@
           <t>NPA, OSBA; NPH-D1+OSBA</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -7103,7 +6425,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>289-981-0564</t>
@@ -7119,7 +6440,6 @@
           <t>rsbassociation.ca</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -7130,15 +6450,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7161,7 +6477,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>647-641-1518</t>
@@ -7172,8 +6487,6 @@
           <t>rwibasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -7184,15 +6497,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7215,11 +6524,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -7230,15 +6534,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7296,15 +6596,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7327,15 +6623,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>renevillavecer@yahoo.com</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>Elite</t>
@@ -7346,15 +6638,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7382,7 +6670,6 @@
           <t>Vaughan, ON</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>info@sc-academy.ca</t>
@@ -7408,15 +6695,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7439,11 +6722,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>Girls Rep</t>
@@ -7454,15 +6732,11 @@
           <t>NPH Showcase Girls</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7520,15 +6794,11 @@
           <t>NPA, NPH Showcase</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7586,15 +6856,11 @@
           <t>NPH Showcase; NJC</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7617,7 +6883,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>519-498-2703</t>
@@ -7648,15 +6913,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7679,7 +6940,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>416-725-8226</t>
@@ -7695,7 +6955,6 @@
           <t>miltonbasketball.ca</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -7706,15 +6965,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7757,7 +7012,6 @@
           <t>sanctuarysports.ca</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -7768,15 +7022,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7799,11 +7049,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -7814,15 +7059,11 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7845,11 +7086,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>Prep program</t>
@@ -7860,15 +7096,11 @@
           <t>NJC</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7891,11 +7123,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -7906,15 +7133,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7937,11 +7160,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -7952,15 +7170,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7983,7 +7197,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>647-834-1424</t>
@@ -8014,9 +7227,6 @@
           <t>NPH Showcase; NPH-SL</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -8049,9 +7259,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>undergroundbasketballclub.ca</t>
@@ -8072,15 +7279,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8103,15 +7306,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>https://vanguardnorthbasketball.ca/</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -8122,15 +7321,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8153,8 +7348,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>renevillavecer@yahoo.com</t>
@@ -8180,15 +7373,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8211,11 +7400,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -8226,15 +7410,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8257,10 +7437,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Nick Wiggins | Founder &amp; CEO</t>
@@ -8276,9 +7452,6 @@
           <t>NPH Showcase; NJC+NPH-SL+NSC</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -8311,11 +7484,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>Academy</t>
@@ -8326,15 +7494,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8372,8 +7536,6 @@
           <t>g_cbasketball@yahoo.ca</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>Rep, Elite</t>
@@ -8384,15 +7546,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8415,11 +7573,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -8430,15 +7583,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8461,8 +7610,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>yvybball@gmail.com</t>
@@ -8473,7 +7620,6 @@
           <t>https://yvybasketball.com/</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -8484,15 +7630,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8550,15 +7692,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8581,7 +7719,6 @@
           <t>Ontario-wide</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>647-703-2691</t>
@@ -8612,15 +7749,11 @@
           <t>AAU</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8648,13 +7781,11 @@
           <t>908-3969 Kingston Rd</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>admin@uplaycanada.com</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Dwayne Washington - CEO/Director</t>
@@ -8670,9 +7801,6 @@
           <t>Nike EYBL</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -8740,15 +7868,11 @@
           <t>OSBA</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8791,16 +7915,11 @@
           <t>https://www.gsquad.us/</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>Rep, Development</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -8863,10 +7982,6 @@
           <t>House league, Camps, Ages 7-17</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -8904,7 +8019,6 @@
           <t>Kingsway College Athletic Complex, 1200 Leland Rd, Oshawa, ON L1K 2H5</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
           <t>via website</t>
@@ -8915,16 +8029,11 @@
           <t>https://www.rumibasketball.com/</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>Camps, Leagues, Ages 11-14</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -8972,7 +8081,6 @@
           <t>admissions@ashbury.ca</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>Norman Southward - Head of School</t>
@@ -8988,15 +8096,11 @@
           <t>NSC</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9054,15 +8158,11 @@
           <t>OSBA, NSC; NPH-SL+OSBA</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9090,14 +8190,11 @@
           <t>P.O. Box 35150 Westgate</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>http://ottawaelite.org/</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>Prep program</t>
@@ -9108,15 +8205,11 @@
           <t>NSC</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9174,15 +8267,11 @@
           <t>NPH Showcase; JUEL</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9240,15 +8329,11 @@
           <t>NSC, NJC</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9291,22 +8376,16 @@
           <t>https://www.17basketball.com/</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>Club teams</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9329,8 +8408,6 @@
           <t>Scarborough</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
           <t>via website</t>
@@ -9356,15 +8433,11 @@
           <t>AAU; NSC</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9422,15 +8495,11 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9463,7 +8532,6 @@
           <t>647-693-8929</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>https://v3prepbasketball.ca/</t>
@@ -9484,15 +8552,11 @@
           <t>OSBA, NSC, NJC</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9515,7 +8579,6 @@
           <t>Simcoe</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>705-717-6449</t>
@@ -9531,7 +8594,6 @@
           <t>simcoeunitedbasketball.com</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -9542,15 +8604,11 @@
           <t>NJC, NPH Showcase</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9583,7 +8641,6 @@
           <t>905-684-1889</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>https://www.ridleycollege.com/</t>
@@ -9604,9 +8661,6 @@
           <t>NPA, OSBA, NSC</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -9649,13 +8703,11 @@
           <t>905-646-2002</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>https://www.stfrancisphoenix.com/</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>School program</t>
@@ -9666,15 +8718,11 @@
           <t>NSC</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9697,11 +8745,6 @@
           <t>Stoney Creek</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -9712,15 +8755,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9743,8 +8782,6 @@
           <t>Toronto</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
           <t>416basketballto@gmail.com</t>
@@ -9755,7 +8792,6 @@
           <t>416basketball.com</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -9766,15 +8802,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9832,9 +8864,6 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -9877,7 +8906,6 @@
           <t>613-797-2089</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>https://canadatopflight.com/</t>
@@ -9898,9 +8926,6 @@
           <t>OSBA, NSC, NJC</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -9963,16 +8988,11 @@
           <t>Training</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10030,9 +9050,6 @@
           <t>OSBA</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -10075,7 +9092,6 @@
           <t>416-391-1441</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
           <t>https://www.crestwood.on.ca/</t>
@@ -10096,9 +9112,6 @@
           <t>NPA, OSBA, NSC</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -10131,7 +9144,6 @@
           <t>Toronto</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>(416) 272-0376</t>
@@ -10157,10 +9169,6 @@
           <t>AAU, Scholarship pathway</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -10193,7 +9201,6 @@
           <t>Toronto</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>(905) 928-2174</t>
@@ -10224,15 +9231,11 @@
           <t>AAU</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10290,15 +9293,11 @@
           <t>NSC</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10356,15 +9355,11 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10422,15 +9417,11 @@
           <t>NPA, OSBA</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10488,15 +9479,11 @@
           <t>OBA, AAU</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10539,7 +9526,6 @@
           <t>https://www.torontotoptier.com/</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>House league, Rep, Training</t>
@@ -10550,15 +9536,11 @@
           <t>NPH-SL</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10586,7 +9568,6 @@
           <t>55 Gordon St Suite 2A, Toronto</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
           <t>via website</t>
@@ -10612,9 +9593,6 @@
           <t>Coalition</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -10677,10 +9655,6 @@
           <t>Youth basketball, Ages 13-24</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -10718,7 +9692,6 @@
           <t>520 Cosburn Ave, East York, Ontario, M4J 2P1</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
           <t>via website</t>
@@ -10744,15 +9717,11 @@
           <t>OBA; Coalition+OBL</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10775,8 +9744,6 @@
           <t>Toronto (GTA-wide)</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
           <t>ciabounce@gmail.com</t>
@@ -10802,9 +9769,6 @@
           <t>Nike EYBL</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -10872,9 +9836,6 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -10937,16 +9898,11 @@
           <t>Performance training academy</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11004,9 +9960,6 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -11059,7 +10012,6 @@
           <t>https://vaughanpanthersbasketball.com</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -11070,15 +10022,11 @@
           <t>NPH Showcase; Coalition+NPH-SL+OBL</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11116,7 +10064,6 @@
           <t>vaughan.ss@yrdsb.ca</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>Maria Maiato, Principal</t>
@@ -11132,9 +10079,6 @@
           <t>OSBA</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -11202,15 +10146,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11233,13 +10173,11 @@
           <t>Waterloo</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>(519) 574-4493</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
           <t>https://waterloowolverines.com</t>
@@ -11260,9 +10198,6 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
@@ -11295,8 +10230,6 @@
           <t>Whitby</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
           <t>via website</t>
@@ -11307,22 +10240,16 @@
           <t>https://www.whitbysaints.com/</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11350,7 +10277,6 @@
           <t>1020 Dryden Blvd, Whitby, ON</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
           <t>via website</t>
@@ -11361,22 +10287,16 @@
           <t>https://www.whitbywildcatsports.ca/</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>Basketball, Volleyball</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11404,7 +10324,6 @@
           <t>2555 College Ave</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
           <t>info@southwindsorwarriors.com</t>
@@ -11430,15 +10349,11 @@
           <t>OBA</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11466,7 +10381,6 @@
           <t>11870 Solomon St, Windsor, ON</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
           <t>renevillavecer@yahoo.com</t>
@@ -11492,15 +10406,11 @@
           <t>NPH Showcase</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr">
         <is>
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
-      <c r="P188" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P188"/>
@@ -11604,24 +10514,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>102 censused member clubs</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11634,24 +10536,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>29 censused member clubs</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11664,24 +10558,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>27 censused member clubs</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11694,24 +10580,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>22 censused member clubs</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11724,24 +10602,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>21 censused member clubs</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11754,24 +10624,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>20 censused member clubs</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11784,24 +10646,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>11 censused member clubs</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11814,24 +10668,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>8 censused member clubs</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11844,24 +10690,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>7 censused member clubs</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11874,24 +10712,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>5 censused member clubs</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11904,24 +10734,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>4 censused member clubs</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11934,24 +10756,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>3 censused member clubs</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11964,24 +10778,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2 censused member clubs</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11994,24 +10800,16 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2 censused member clubs</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>from club census</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L15"/>
@@ -18703,13 +17501,11 @@
           <t>Ancaster</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>ancastermagic@gmail.com</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>https://www.ancastermagic.ca/</t>
@@ -18737,8 +17533,6 @@
           <t>info@bramptoncityprep.com</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18847,13 +17641,11 @@
           <t>Brampton/Vaughan/Markham/Mississauga/Niagara</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>via website</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>https://www.riseupleague.com/</t>
@@ -18918,7 +17710,6 @@
           <t>Jim Wilson, Chief Executive Officer</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18941,7 +17732,6 @@
           <t>via website</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>https://www.burlingtonbasketball.ca/</t>
@@ -19001,7 +17791,6 @@
           <t>caledoncougarsbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>https://www.caledoncougars.ca/</t>
@@ -19019,13 +17808,11 @@
           <t>Chatham</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>via website</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>http://www.chathamkentwildcats.com/</t>
@@ -19053,7 +17840,6 @@
           <t>via website</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>https://www.durhamcitybasketball.ca/</t>
@@ -19081,7 +17867,6 @@
           <t>contactgatorsacademy@gmail.com</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>www.gatorsbasketballacademy.com</t>
@@ -19141,7 +17926,6 @@
           <t>via website</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>https://www.durhambluesbasketball.com/</t>
@@ -19196,7 +17980,6 @@
           <t>416-393-5540</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>John D'Onofrio, Principal</t>
@@ -19283,13 +18066,11 @@
           <t>GTA-wide</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>via website</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>https://www.girlsplaytoo.ca/aau</t>
@@ -19307,7 +18088,6 @@
           <t>Gatineau</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>info@basketballgatineau.com</t>
@@ -19345,7 +18125,6 @@
           <t>administration@guelphbasketball.com</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>guelphbasketball.com</t>
@@ -19405,7 +18184,6 @@
           <t>admin@lincolnprep.ca</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>https://www.lincolnprep.ca/</t>
@@ -19423,7 +18201,6 @@
           <t>Kingston</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>info@kingstonimpact.ca</t>
@@ -19488,7 +18265,6 @@
           <t>519-621-4050</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Jordan Figueiredo, Principal</t>
@@ -19543,8 +18319,6 @@
           <t>London</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Judy Provenzano, Owner/Director of Operations</t>
@@ -19567,13 +18341,11 @@
           <t>London</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>via website</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>https://www.londoncyobasketball.com/</t>
@@ -19591,7 +18363,6 @@
           <t>London</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>via website</t>
@@ -19619,8 +18390,6 @@
           <t>London</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Kevin Barnes, Head Coach</t>
@@ -19749,7 +18518,6 @@
           <t>info@CKATT.com</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>ckatt.com</t>
@@ -19777,7 +18545,6 @@
           <t>info@mmba.on.ca</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>http://www.mmba.on.ca/</t>
@@ -19965,7 +18732,6 @@
           <t>blueprint_training@hotmail.com</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>https://blueprintbasketball.ca/</t>
@@ -19983,7 +18749,6 @@
           <t>Niagara Falls</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>info@niagaraprepbasketball.com</t>
@@ -20171,13 +18936,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>info@4qt.ca</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>4qt.ca</t>
@@ -20195,13 +18958,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>register@ball905.com</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>ball905rep.com</t>
@@ -20224,7 +18985,6 @@
           <t>905-389-7834</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>John Rocchi | President</t>
@@ -20257,7 +19017,6 @@
           <t>shawn@vidasana.ca</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>https://www.cbelite.ca/</t>
@@ -20275,8 +19034,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>Junior Cadougan, Founder</t>
@@ -20309,8 +19066,6 @@
           <t>northernkingsacademy@gmail.com</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -20323,13 +19078,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>cmeelitebasketball23@gmail.com</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>cmeelitebasketball.com</t>
@@ -20357,7 +19110,6 @@
           <t>via website</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>https://www.corecityhoops.com/</t>
@@ -20407,8 +19159,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>Adrian Sapp, Founder/Head Coach</t>
@@ -20441,7 +19191,6 @@
           <t>info@elevationathletics.ca</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>https://elevationathletics.ca</t>
@@ -20464,7 +19213,6 @@
           <t>(647) 879-8344</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Boris Bakovic</t>
@@ -20487,13 +19235,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>info@excelhoops.com</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>https://www.excelhoops.com/</t>
@@ -20511,14 +19257,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Jermaine Lyle</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -20531,14 +19274,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Jermaine Lyle | Founder; Sheldon McIntosh | Coach</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -20551,13 +19291,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>info@lasalleguardiansbasketball.com</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>https://lasalleguardiansbasketball.com/</t>
@@ -20575,7 +19313,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>h5academy@h5f.ca</t>
@@ -20603,7 +19340,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>HQelitecanada1@gmail.com</t>
@@ -20710,7 +19446,6 @@
           <t>Terry House Jr., Program Director</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -20733,7 +19468,6 @@
           <t>info@kingheightsacademy.com</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>https://kingheightsacademy.com/</t>
@@ -20788,7 +19522,6 @@
           <t>647-945-6945</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>Michael Sousa, President</t>
@@ -20843,7 +19576,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>norwoodstarsbasketball@gmail.com</t>
@@ -20854,7 +19586,6 @@
           <t>Jenieve Grant | Director</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -20931,7 +19662,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>polarisprepacademy@gmail.com</t>
@@ -20969,7 +19699,6 @@
           <t>rsbelite@gmail.com</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>rsbassociation.ca</t>
@@ -20997,8 +19726,6 @@
           <t>rwibasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -21043,14 +19770,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>renevillavecer@yahoo.com</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -21063,7 +19787,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>info@sc-academy.ca</t>
@@ -21197,7 +19920,6 @@
           <t>info@miltonbasketball.ca</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>miltonbasketball.ca</t>
@@ -21225,7 +19947,6 @@
           <t>contact@sanctuarysportcenter.ca</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>sanctuarysports.ca</t>
@@ -21275,8 +19996,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Jeremy Granger, Director/Head Coach</t>
@@ -21299,7 +20018,6 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>renevillavecer@yahoo.com</t>
@@ -21327,14 +20045,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Nick Wiggins | Founder &amp; CEO</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -21357,8 +20072,6 @@
           <t>g_cbasketball@yahoo.ca</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -21371,13 +20084,11 @@
           <t>Ontario</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>yvybball@gmail.com</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>https://yvybasketball.com/</t>
@@ -21459,7 +20170,6 @@
           <t>Ontario-wide</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>admin@uplaycanada.com</t>
@@ -21470,7 +20180,6 @@
           <t>Dwayne Washington - CEO/Director</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -21525,7 +20234,6 @@
           <t>gladiatorsbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>https://www.gsquad.us/</t>
@@ -21575,13 +20283,11 @@
           <t>Oshawa/Whitby/Durham</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>via website</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>https://www.rumibasketball.com/</t>
@@ -21614,7 +20320,6 @@
           <t>Norman Southward - Head of School</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -21733,7 +20438,6 @@
           <t>via website</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>https://www.17basketball.com/</t>
@@ -21751,7 +20455,6 @@
           <t>Scarborough</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>via website</t>
@@ -21816,7 +20519,6 @@
           <t>647-693-8929</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Keir Bryan, Director</t>
@@ -21849,7 +20551,6 @@
           <t>info@simcoeunitedbasketball.com</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>simcoeunitedbasketball.com</t>
@@ -21872,7 +20573,6 @@
           <t>905-684-1889</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>J. Edward Kidd, Headmaster</t>
@@ -21900,8 +20600,6 @@
           <t>905-646-2002</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>https://www.stfrancisphoenix.com/</t>
@@ -21919,13 +20617,11 @@
           <t>Toronto</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>416basketballto@gmail.com</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>416basketball.com</t>
@@ -21980,7 +20676,6 @@
           <t>613-797-2089</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>Tony House, Founder &amp; Head Coach</t>
@@ -22072,7 +20767,6 @@
           <t>416-391-1441</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>Dave Hecock, Head of School (Upper School)</t>
@@ -22297,7 +20991,6 @@
           <t>via website</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>https://www.torontotoptier.com/</t>
@@ -22315,7 +21008,6 @@
           <t>Toronto</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>via website</t>
@@ -22375,7 +21067,6 @@
           <t>Toronto (East/Beaches)</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>via website</t>
@@ -22403,7 +21094,6 @@
           <t>Toronto (GTA-wide)</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>ciabounce@gmail.com</t>
@@ -22537,7 +21227,6 @@
           <t>info@vaughanbasketball.com</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>https://vaughanpanthersbasketball.com</t>
@@ -22570,7 +21259,6 @@
           <t>Maria Maiato, Principal</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -22620,7 +21308,6 @@
           <t>(519) 574-4493</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>Chad McPhearson, Director</t>
@@ -22643,13 +21330,11 @@
           <t>Whitby</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>via website</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>https://www.whitbysaints.com/</t>
@@ -22667,13 +21352,11 @@
           <t>Whitby/Oshawa/Ajax</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>via website</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>https://www.whitbywildcatsports.ca/</t>
@@ -22691,7 +21374,6 @@
           <t>Windsor</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>info@southwindsorwarriors.com</t>
@@ -22719,7 +21401,6 @@
           <t>Windsor</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>renevillavecer@yahoo.com</t>
@@ -22740,4 +21421,2351 @@
   <autoFilter ref="A1:F142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D129"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Elite team entries (2025-26)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Breakdown (league=entries)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dragons de Gatineau</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1)=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Royal Crown</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1 + NPA + WNPA)=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brampton City Prep</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NJC=2; NSC=1; OSBA-coalition=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Wiggins Elite</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NPH(SL)=4; NJC=2; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C.O.D.E Academy</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NJC=1; OSBA-coalition=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FEIA (Fort Erie)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1 + NPA + WNPA)=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ottawa Elite (incl. Prep)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1)=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>St. Jude's Prep/Academy</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NPH(D1 + NPA + WNPA)=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lincoln Prep</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NPH(D1 + NPA)=2; OSBA-coalition=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PDM Basketball</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1)=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hodan Prep</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NPH(D1 + NPA)=2; OSBA-coalition=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>St. Jude's Academy</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Burloak Elite</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NPH(SL)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CE23 Academy</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NPH(SL)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NDL</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NPH(D1)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>North York Lions</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NPH(SL)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RWI</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NPH(SL)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Underdog Elite</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NPH(SL)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>City Above Elite</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NPH(SL)=3; NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tall Pines Academy</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NPH(D1)=3; OSBA-coalition=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Toronto Lords</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1)=3; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ONL-X</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1)=2; NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Canada Topflight Academy</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NJC=1; OSBA-coalition=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Future Hope Academy</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NJC=1; OSBA-coalition=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Simcoe United</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NJC=2; NSC=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>William Academy</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NJC=1; OSBA-coalition=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Royal Crown School</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Crestwood Prep</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Orangeville Prep / Athlete Institute</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Victory Academy / Victory Prep</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CKATT Basketball</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NPH(SL)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Dropoff Elite</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Edge School (Calgary)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NPH(D1 + NPA + WNPA)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M and R Basketball</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NPH(SL)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MC Elite</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NPH(SL)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Polaris Prep</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NPH(D1 + NPA)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SC Academy</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Simcoe United Spartans</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NPH(SL)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TNP</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Tri-City (Prep/Academy)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NPH(D1 + NPA)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Vanguard North Prep</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NPH(SL)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Westfield Secondary</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Brotherhood Elite</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>G2S Game Changers</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2; NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tru Balance</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2; NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Full Circle Basketball Academy</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1; OSBA-coalition=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SC Academy Prep</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SSF Blizzard</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NJC=2; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tri-City Prep</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NJC=1; OSBA-coalition=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Vanguard (North)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Fort Erie International Academy</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Polaris Prep Academy</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>King Heights Academy</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Colts Prep</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Father Henry Carr</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BCP</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NPH(D1 + NPA)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Dynastie</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NPH(D1)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EM Elite</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Eurostep Basketball</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hamilton Transformation Academy</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>King Heights</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NPH(SL + NPA)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kings Court Basketball</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Malton Sting Basketball</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>North Toronto Huskies</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Retro Elite</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>St. Michael's College School</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NPH(SL + D1)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Vaughan Panthers</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Waterloo Wolverines Elite</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>West United Prep</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>YvY Elite</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NPH(SL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Cali Prep</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Compass Academy</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>HQ Prep</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NJC=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Jungle Prep</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LBA</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>London Ramblers</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NJC=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Project Excellence</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SBA Premier</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Top Notch Prep</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NJC=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Westfield Prep</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Wolverines Elite</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Inspire Academy</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Lo-Ellen Park Prep</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Niagara Prep</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>J.Addison School</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Capital Courts Academy</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Louis-Riel</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>H5 Academy</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>James Cardinal McGuigan</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Uchenna Academy</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>506 Elite Jr Academy</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Against The Six Prep</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Alpha Elite</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CKATT</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Collective Elite Academy</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Cooksville We&gt;Me</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Dynamic Basketball</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Eastern Basketball Academy</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Elton Academy</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>F.O.R.M. Basketball Academy</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Gators Basketball Academy</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>GBU</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Ignite Academy</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Kings Court Academy</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>M&amp;R Basketball</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Monarchs</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NSE Select Academy</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Orangeville Prep</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>RSB Elite</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>RWI519</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SCI Spartans</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Ste Cecile Academy</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Strive Hoops</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Team Sanctuary</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Team Thetford</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Top Left</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Triple Balance</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>UEWB</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Ridley College</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Cambridge International Academy</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>King's Christian Collegiate</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Redmond Basketball</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Richmond Hill Ascend Prep</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Ace Acumen Heights</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>AD Rebelles</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Southwest Academy</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>St. Michael's College</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>OSBA-coalition=1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D129"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/research/provinces/SportsHub-Ontario.xlsx
+++ b/docs/research/provinces/SportsHub-Ontario.xlsx
@@ -11,14 +11,14 @@
     <sheet name="Leagues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Club-League Map" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Club Sizes (ON elite)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Club Sizes (ON)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$264</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$142</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Club Sizes (ON elite)'!$A$1:$D$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Club Sizes (ON)'!$A$1:$D$216</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21429,11 +21429,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="58" customWidth="1" min="4" max="4"/>
   </cols>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Elite team entries (2025-26)</t>
+          <t>Censused team entries 2025-26</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -21466,15 +21466,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dragons de Gatineau</t>
+          <t>Scarborough Blues / SBA (Team {coach}, Premier)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NPH(SL + D1)=9</t>
+          <t>Coalition (Summer 2025)=18</t>
         </is>
       </c>
     </row>
@@ -21484,15 +21484,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Royal Crown</t>
+          <t>The MUMBA Mentality</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NPH(SL + D1 + NPA + WNPA)=8</t>
+          <t>Coalition (Summer 2025)=18</t>
         </is>
       </c>
     </row>
@@ -21502,15 +21502,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brampton City Prep</t>
+          <t>YvY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NJC=2; NSC=1; OSBA-coalition=5</t>
+          <t>Coalition (Summer 2025)=12</t>
         </is>
       </c>
     </row>
@@ -21520,15 +21520,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wiggins Elite</t>
+          <t>Toronto Lords</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NPH(SL)=4; NJC=2; NSC=1</t>
+          <t>Coalition (Summer 2025)=7; NPH-SL=2; NSC=1; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -21538,15 +21538,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C.O.D.E Academy</t>
+          <t>Eurostep</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NJC=1; OSBA-coalition=6</t>
+          <t>Coalition (Summer 2025)=11</t>
         </is>
       </c>
     </row>
@@ -21556,15 +21556,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FEIA (Fort Erie)</t>
+          <t>Burloak</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NPH(SL + D1 + NPA + WNPA)=6</t>
+          <t>Coalition (Summer 2025)=10</t>
         </is>
       </c>
     </row>
@@ -21574,15 +21574,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ottawa Elite (incl. Prep)</t>
+          <t>Dragons de Gatineau</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NPH(SL + D1)=6</t>
+          <t>NPH-SL=8; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -21592,15 +21592,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>St. Jude's Prep/Academy</t>
+          <t>Brampton Warriors</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NPH(D1 + NPA + WNPA)=6</t>
+          <t>Coalition (Summer 2025)=9</t>
         </is>
       </c>
     </row>
@@ -21610,15 +21610,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lincoln Prep</t>
+          <t>iDream by BOA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NPH(D1 + NPA)=2; OSBA-coalition=4</t>
+          <t>Coalition (Summer 2025)=9</t>
         </is>
       </c>
     </row>
@@ -21628,15 +21628,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PDM Basketball</t>
+          <t>Born 2 Stand Out</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NPH(SL + D1)=5</t>
+          <t>Coalition (Summer 2025)=9</t>
         </is>
       </c>
     </row>
@@ -21646,15 +21646,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hodan Prep</t>
+          <t>Royal Crown</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NPH(D1 + NPA)=2; OSBA-coalition=3</t>
+          <t>NPH-SL=3; NPH-D1=3; NPA=1; WNPA=1</t>
         </is>
       </c>
     </row>
@@ -21664,15 +21664,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>St. Jude's Academy</t>
+          <t>Durham Blues</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OSBA-coalition=5</t>
+          <t>Coalition (Summer 2025)=8</t>
         </is>
       </c>
     </row>
@@ -21682,15 +21682,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Burloak Elite</t>
+          <t>Wiggins Elite</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NPH(SL)=4</t>
+          <t>NPH-SL=4; NJC=2; NSC=1</t>
         </is>
       </c>
     </row>
@@ -21700,15 +21700,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CE23 Academy</t>
+          <t>City Above</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NPH(SL)=4</t>
+          <t>Coalition (Summer 2025)=7</t>
         </is>
       </c>
     </row>
@@ -21718,15 +21718,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Hoopzone Knights</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NPH(SL + D1)=4</t>
+          <t>Coalition (Summer 2025)=7</t>
         </is>
       </c>
     </row>
@@ -21736,15 +21736,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NDL</t>
+          <t>FEIA (Fort Erie)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NPH(D1)=4</t>
+          <t>NPH-D1=3; NPH-SL=1; NPA=1; WNPA=1</t>
         </is>
       </c>
     </row>
@@ -21754,15 +21754,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>North York Lions</t>
+          <t>Ottawa Elite (incl. Prep)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NPH(SL)=4</t>
+          <t>NPH-SL=4; NPH-D1=2</t>
         </is>
       </c>
     </row>
@@ -21772,15 +21772,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RWI</t>
+          <t>St. Jude's Prep/Academy</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NPH(SL)=4</t>
+          <t>NPH-D1=4; NPA=1; WNPA=1</t>
         </is>
       </c>
     </row>
@@ -21790,15 +21790,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Underdog Elite</t>
+          <t>Lincoln Prep</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NPH(SL)=4</t>
+          <t>OSBA=4; NPH-D1=1; NPA=1</t>
         </is>
       </c>
     </row>
@@ -21808,15 +21808,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>City Above Elite</t>
+          <t>C.O.D.E. Academy (Provincial + International)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NPH(SL)=3; NJC=1</t>
+          <t>OSBA=6</t>
         </is>
       </c>
     </row>
@@ -21826,15 +21826,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tall Pines Academy</t>
+          <t>Future Hope Academy</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NPH(D1)=3; OSBA-coalition=1</t>
+          <t>OSBA=3; NJC=1; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -21844,15 +21844,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Toronto Lords</t>
+          <t>Monarchs</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NPH(SL + D1)=3; NSC=1</t>
+          <t>Coalition (Summer 2025)=4; NSC=1</t>
         </is>
       </c>
     </row>
@@ -21862,15 +21862,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ONL-X</t>
+          <t>PDM Basketball</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NPH(SL + D1)=2; NJC=1; NSC=1</t>
+          <t>NPH-SL=4; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -21880,15 +21880,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Canada Topflight Academy</t>
+          <t>St. Jude's Academy (Blue + White in Trillium)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NJC=1; OSBA-coalition=3</t>
+          <t>OSBA=5</t>
         </is>
       </c>
     </row>
@@ -21898,15 +21898,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Future Hope Academy</t>
+          <t>Brampton City Prep (Nat/Prov + Reg/North + South)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NJC=1; OSBA-coalition=3</t>
+          <t>OSBA=5</t>
         </is>
       </c>
     </row>
@@ -21916,15 +21916,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Simcoe United</t>
+          <t>YNBA (incl. Avengers)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NJC=2; NSC=2</t>
+          <t>Coalition (Summer 2025)=5</t>
         </is>
       </c>
     </row>
@@ -21934,7 +21934,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>William Academy</t>
+          <t>City Above Elite</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NJC=1; OSBA-coalition=3</t>
+          <t>NPH-SL=3; NJC=1</t>
         </is>
       </c>
     </row>
@@ -21952,7 +21952,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Royal Crown School</t>
+          <t>ONL-X</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OSBA-coalition=4</t>
+          <t>NJC=1; NSC=1; NPH-SL=1; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -21970,7 +21970,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Crestwood Prep</t>
+          <t>Simcoe United</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OSBA-coalition=4</t>
+          <t>NJC=2; NSC=2</t>
         </is>
       </c>
     </row>
@@ -21988,7 +21988,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Orangeville Prep / Athlete Institute</t>
+          <t>Burloak Elite</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -21996,7 +21996,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OSBA-coalition=4</t>
+          <t>NPH-SL=4</t>
         </is>
       </c>
     </row>
@@ -22006,7 +22006,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Victory Academy / Victory Prep</t>
+          <t>CE23 Academy</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -22014,7 +22014,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>OSBA-coalition=4</t>
+          <t>NPH-SL=4</t>
         </is>
       </c>
     </row>
@@ -22024,15 +22024,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CKATT Basketball</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NPH(SL)=3</t>
+          <t>NPH-SL=2; NPH-D1=2</t>
         </is>
       </c>
     </row>
@@ -22042,15 +22042,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dropoff Elite</t>
+          <t>NDL</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NPH(SL + D1)=3</t>
+          <t>NPH-SL=3; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -22060,15 +22060,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Edge School (Calgary)</t>
+          <t>North York Lions</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NPH(D1 + NPA + WNPA)=3</t>
+          <t>NPH-SL=4</t>
         </is>
       </c>
     </row>
@@ -22078,15 +22078,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>M and R Basketball</t>
+          <t>RWI</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NPH(SL)=3</t>
+          <t>NPH-SL=4</t>
         </is>
       </c>
     </row>
@@ -22096,15 +22096,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MC Elite</t>
+          <t>Underdog Elite</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NPH(SL)=3</t>
+          <t>NPH-SL=4</t>
         </is>
       </c>
     </row>
@@ -22114,15 +22114,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Polaris Prep</t>
+          <t>Tall Pines Academy</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NPH(D1 + NPA)=3</t>
+          <t>NPH-SL=2; NPH-D1=1; OSBA=1</t>
         </is>
       </c>
     </row>
@@ -22132,15 +22132,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SC Academy</t>
+          <t>Royal Crown School</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NPH(SL + D1)=3</t>
+          <t>OSBA=4</t>
         </is>
       </c>
     </row>
@@ -22150,15 +22150,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Simcoe United Spartans</t>
+          <t>Crestwood Prep (incl. Blue in W)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NPH(SL)=3</t>
+          <t>OSBA=4</t>
         </is>
       </c>
     </row>
@@ -22168,15 +22168,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TNP</t>
+          <t>Orangeville Prep / Athlete Institute</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NPH(SL + D1)=3</t>
+          <t>OSBA=4</t>
         </is>
       </c>
     </row>
@@ -22186,15 +22186,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tri-City (Prep/Academy)</t>
+          <t>Victory Academy / Victory Prep (East + West)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NPH(D1 + NPA)=3</t>
+          <t>OSBA=4</t>
         </is>
       </c>
     </row>
@@ -22204,15 +22204,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vanguard North Prep</t>
+          <t>East York Eagles</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NPH(SL)=3</t>
+          <t>Coalition (Summer 2025)=4</t>
         </is>
       </c>
     </row>
@@ -22222,7 +22222,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Westfield Secondary</t>
+          <t>Brampton City Prep</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -22230,7 +22230,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NPH(SL + D1)=3</t>
+          <t>NJC=2; NSC=1</t>
         </is>
       </c>
     </row>
@@ -22248,7 +22248,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NPH(SL)=2; NSC=1</t>
+          <t>NPH-SL=2; NSC=1</t>
         </is>
       </c>
     </row>
@@ -22258,7 +22258,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>G2S Game Changers</t>
+          <t>Full Circle Basketball Academy</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -22266,7 +22266,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NPH(SL)=2; NJC=1</t>
+          <t>NJC=1; NSC=1; OSBA=1</t>
         </is>
       </c>
     </row>
@@ -22276,7 +22276,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tru Balance</t>
+          <t>G2S Game Changers</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -22284,7 +22284,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NPH(SL)=2; NJC=1</t>
+          <t>NPH-SL=2; NJC=1</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Full Circle Basketball Academy</t>
+          <t>SC Academy Prep</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -22302,7 +22302,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NJC=1; NSC=1; OSBA-coalition=1</t>
+          <t>NSC=2; NJC=1</t>
         </is>
       </c>
     </row>
@@ -22312,7 +22312,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SC Academy Prep</t>
+          <t>SSF Blizzard</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -22320,7 +22320,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NJC=1; NSC=2</t>
+          <t>NJC=2; NSC=1</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SSF Blizzard</t>
+          <t>Tri-City Prep</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NJC=2; NSC=1</t>
+          <t>OSBA=2; NJC=1</t>
         </is>
       </c>
     </row>
@@ -22348,7 +22348,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tri-City Prep</t>
+          <t>Tru Balance</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -22356,7 +22356,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NJC=1; OSBA-coalition=2</t>
+          <t>NPH-SL=2; NJC=1</t>
         </is>
       </c>
     </row>
@@ -22374,7 +22374,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NJC=1; NSC=2</t>
+          <t>NSC=2; NJC=1</t>
         </is>
       </c>
     </row>
@@ -22384,7 +22384,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fort Erie International Academy</t>
+          <t>CKATT Basketball</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OSBA-coalition=3</t>
+          <t>NPH-SL=3</t>
         </is>
       </c>
     </row>
@@ -22402,7 +22402,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Polaris Prep Academy</t>
+          <t>Dropoff Elite</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -22410,7 +22410,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OSBA-coalition=3</t>
+          <t>NPH-SL=2; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -22420,7 +22420,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>King Heights Academy</t>
+          <t>Edge School (Calgary)</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -22428,7 +22428,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OSBA-coalition=3</t>
+          <t>NPH-D1=1; NPA=1; WNPA=1</t>
         </is>
       </c>
     </row>
@@ -22438,7 +22438,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Colts Prep</t>
+          <t>M and R Basketball</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -22446,7 +22446,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OSBA-coalition=3</t>
+          <t>NPH-SL=3</t>
         </is>
       </c>
     </row>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Father Henry Carr</t>
+          <t>MC Elite</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OSBA-coalition=3</t>
+          <t>NPH-SL=3</t>
         </is>
       </c>
     </row>
@@ -22474,15 +22474,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BCP</t>
+          <t>Polaris Prep</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NPH(D1 + NPA)=2</t>
+          <t>NPH-D1=2; NPA=1</t>
         </is>
       </c>
     </row>
@@ -22492,15 +22492,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dynastie</t>
+          <t>SC Academy</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NPH(D1)=2</t>
+          <t>NPH-SL=2; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -22510,15 +22510,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EM Elite</t>
+          <t>Simcoe United Spartans</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NPH(SL)=2</t>
+          <t>NPH-SL=3</t>
         </is>
       </c>
     </row>
@@ -22528,15 +22528,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eurostep Basketball</t>
+          <t>TNP</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NPH(SL)=2</t>
+          <t>NPH-SL=2; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -22546,15 +22546,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hamilton Transformation Academy</t>
+          <t>Tri-City (Prep/Academy)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NPH(SL)=2</t>
+          <t>NPH-D1=2; NPA=1</t>
         </is>
       </c>
     </row>
@@ -22564,15 +22564,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>King Heights</t>
+          <t>Vanguard North Prep</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NPH(SL + NPA)=2</t>
+          <t>NPH-SL=3</t>
         </is>
       </c>
     </row>
@@ -22582,15 +22582,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kings Court Basketball</t>
+          <t>Westfield Secondary</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NPH(SL)=2</t>
+          <t>NPH-D1=2; NPH-SL=1</t>
         </is>
       </c>
     </row>
@@ -22600,15 +22600,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Malton Sting Basketball</t>
+          <t>Vaughan Panthers</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NPH(SL)=2</t>
+          <t>NPH-SL=2; Coalition (Summer 2025)=1</t>
         </is>
       </c>
     </row>
@@ -22618,15 +22618,15 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>North Toronto Huskies</t>
+          <t>James Cardinal McGuigan</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NPH(SL)=2</t>
+          <t>OSBA=2; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -22636,15 +22636,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Retro Elite</t>
+          <t>Niagara Prep</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NPH(SL)=2</t>
+          <t>OSBA=2; WNPA=1</t>
         </is>
       </c>
     </row>
@@ -22654,15 +22654,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>St. Michael's College School</t>
+          <t>Uchenna Academy</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NPH(SL + D1)=2</t>
+          <t>OSBA=2; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -22672,15 +22672,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vaughan Panthers</t>
+          <t>Fort Erie International Academy</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NPH(SL)=2</t>
+          <t>OSBA=3</t>
         </is>
       </c>
     </row>
@@ -22690,15 +22690,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Waterloo Wolverines Elite</t>
+          <t>Hodan Prep (incl. Nighthawks)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NPH(SL)=2</t>
+          <t>OSBA=3</t>
         </is>
       </c>
     </row>
@@ -22708,15 +22708,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>West United Prep</t>
+          <t>William Academy (incl. Cobourg)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NPH(SL)=2</t>
+          <t>OSBA=3</t>
         </is>
       </c>
     </row>
@@ -22726,15 +22726,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YvY Elite</t>
+          <t>Canada Topflight Academy (Gold + Red)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NPH(SL)=2</t>
+          <t>OSBA=3</t>
         </is>
       </c>
     </row>
@@ -22744,15 +22744,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cali Prep</t>
+          <t>Polaris Prep Academy (Gold + Black)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NJC=1; NSC=1</t>
+          <t>OSBA=3</t>
         </is>
       </c>
     </row>
@@ -22762,15 +22762,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Compass Academy</t>
+          <t>King Heights Academy</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NJC=1; NSC=1</t>
+          <t>OSBA=3</t>
         </is>
       </c>
     </row>
@@ -22780,15 +22780,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HQ Prep</t>
+          <t>Colts Prep</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NJC=2</t>
+          <t>OSBA=3</t>
         </is>
       </c>
     </row>
@@ -22798,15 +22798,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jungle Prep</t>
+          <t>Father Henry Carr (Jr. Prep + Freshmen Prep)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NJC=1; NSC=1</t>
+          <t>OSBA=3</t>
         </is>
       </c>
     </row>
@@ -22816,7 +22816,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LBA</t>
+          <t>Alpha Elite</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -22824,7 +22824,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NJC=1; NSC=1</t>
+          <t>NJC=1; NPH-SL=1</t>
         </is>
       </c>
     </row>
@@ -22834,7 +22834,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>London Ramblers</t>
+          <t>Cali Prep</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NJC=2</t>
+          <t>NJC=1; NSC=1</t>
         </is>
       </c>
     </row>
@@ -22852,7 +22852,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Project Excellence</t>
+          <t>Compass Academy</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -22870,7 +22870,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SBA Premier</t>
+          <t>Eastern Basketball Academy</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -22878,7 +22878,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NJC=1; NSC=1</t>
+          <t>NJC=1; NPH-SL=1</t>
         </is>
       </c>
     </row>
@@ -22888,7 +22888,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Top Notch Prep</t>
+          <t>HQ Prep</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -22906,7 +22906,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Westfield Prep</t>
+          <t>Jungle Prep</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -22924,7 +22924,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Wolverines Elite</t>
+          <t>LBA</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -22942,7 +22942,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Inspire Academy</t>
+          <t>London Ramblers</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OSBA-coalition=2</t>
+          <t>NJC=2</t>
         </is>
       </c>
     </row>
@@ -22960,7 +22960,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lo-Ellen Park Prep</t>
+          <t>Orangeville Prep</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>OSBA-coalition=2</t>
+          <t>NSC=1; NPH-SL=1</t>
         </is>
       </c>
     </row>
@@ -22978,7 +22978,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Niagara Prep</t>
+          <t>Project Excellence</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -22986,7 +22986,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OSBA-coalition=2</t>
+          <t>NJC=1; NSC=1</t>
         </is>
       </c>
     </row>
@@ -22996,7 +22996,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>J.Addison School</t>
+          <t>SBA Premier</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -23004,7 +23004,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>OSBA-coalition=2</t>
+          <t>NJC=1; NSC=1</t>
         </is>
       </c>
     </row>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capital Courts Academy</t>
+          <t>Ste Cecile Academy</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -23022,7 +23022,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>OSBA-coalition=2</t>
+          <t>NSC=1; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -23032,7 +23032,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Louis-Riel</t>
+          <t>Top Notch Prep</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>OSBA-coalition=2</t>
+          <t>NJC=2</t>
         </is>
       </c>
     </row>
@@ -23050,7 +23050,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>H5 Academy</t>
+          <t>Westfield Prep</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>OSBA-coalition=2</t>
+          <t>NJC=1; NSC=1</t>
         </is>
       </c>
     </row>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>James Cardinal McGuigan</t>
+          <t>Wolverines Elite</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>OSBA-coalition=2</t>
+          <t>NJC=1; NSC=1</t>
         </is>
       </c>
     </row>
@@ -23086,7 +23086,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Uchenna Academy</t>
+          <t>BCP</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>OSBA-coalition=2</t>
+          <t>NPH-D1=1; NPA=1</t>
         </is>
       </c>
     </row>
@@ -23104,15 +23104,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>506 Elite Jr Academy</t>
+          <t>Dynastie</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>NPH-D1=2</t>
         </is>
       </c>
     </row>
@@ -23122,15 +23122,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Against The Six Prep</t>
+          <t>EM Elite</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>NPH-SL=2</t>
         </is>
       </c>
     </row>
@@ -23140,15 +23140,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Alpha Elite</t>
+          <t>Eurostep Basketball</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>NPH-SL=2</t>
         </is>
       </c>
     </row>
@@ -23158,15 +23158,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CKATT</t>
+          <t>Hamilton Transformation Academy</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>NPH-SL=2</t>
         </is>
       </c>
     </row>
@@ -23176,15 +23176,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Collective Elite Academy</t>
+          <t>Hodan Prep</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>NPH-D1=1; NPA=1</t>
         </is>
       </c>
     </row>
@@ -23194,15 +23194,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cooksville We&gt;Me</t>
+          <t>King Heights</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>NPH-SL=1; NPA=1</t>
         </is>
       </c>
     </row>
@@ -23212,15 +23212,15 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dynamic Basketball</t>
+          <t>Kings Court Basketball</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NSC=1</t>
+          <t>NPH-SL=2</t>
         </is>
       </c>
     </row>
@@ -23230,15 +23230,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Eastern Basketball Academy</t>
+          <t>Malton Sting Basketball</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>NPH-SL=2</t>
         </is>
       </c>
     </row>
@@ -23248,15 +23248,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Elton Academy</t>
+          <t>North Toronto Huskies</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NSC=1</t>
+          <t>NPH-SL=2</t>
         </is>
       </c>
     </row>
@@ -23266,15 +23266,15 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>F.O.R.M. Basketball Academy</t>
+          <t>Retro Elite</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NSC=1</t>
+          <t>NPH-SL=2</t>
         </is>
       </c>
     </row>
@@ -23284,15 +23284,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Gators Basketball Academy</t>
+          <t>St. Michael's College School</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NSC=1</t>
+          <t>NPH-SL=1; NPH-D1=1</t>
         </is>
       </c>
     </row>
@@ -23302,15 +23302,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GBU</t>
+          <t>Waterloo Wolverines Elite</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NSC=1</t>
+          <t>NPH-SL=2</t>
         </is>
       </c>
     </row>
@@ -23320,15 +23320,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ignite Academy</t>
+          <t>West United Prep</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>NPH-SL=2</t>
         </is>
       </c>
     </row>
@@ -23338,15 +23338,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kings Court Academy</t>
+          <t>YvY Elite</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>NPH-SL=2</t>
         </is>
       </c>
     </row>
@@ -23356,15 +23356,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>M&amp;R Basketball</t>
+          <t>King's Christian Collegiate</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NSC=1</t>
+          <t>WNPA=1; OSBA=1</t>
         </is>
       </c>
     </row>
@@ -23374,15 +23374,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Monarchs</t>
+          <t>Ridley College</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NSC=1</t>
+          <t>NPA=1; OSBA=1</t>
         </is>
       </c>
     </row>
@@ -23392,15 +23392,15 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NSE Select Academy</t>
+          <t>Southwest Academy</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>NPH-D1=1; OSBA=1</t>
         </is>
       </c>
     </row>
@@ -23410,15 +23410,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Orangeville Prep</t>
+          <t>Inspire Academy</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NSC=1</t>
+          <t>OSBA=2</t>
         </is>
       </c>
     </row>
@@ -23428,15 +23428,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RSB Elite</t>
+          <t>Lo-Ellen Park Prep</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>OSBA=2</t>
         </is>
       </c>
     </row>
@@ -23446,15 +23446,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RWI519</t>
+          <t>J.Addison School</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>OSBA=2</t>
         </is>
       </c>
     </row>
@@ -23464,15 +23464,15 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SCI Spartans</t>
+          <t>Capital Courts Academy</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>OSBA=2</t>
         </is>
       </c>
     </row>
@@ -23482,15 +23482,15 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ste Cecile Academy</t>
+          <t>Louis-Riel (Academy)</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NSC=1</t>
+          <t>OSBA=2</t>
         </is>
       </c>
     </row>
@@ -23500,15 +23500,15 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Strive Hoops</t>
+          <t>H5 Academy</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>OSBA=2</t>
         </is>
       </c>
     </row>
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Team Sanctuary</t>
+          <t>Durham Rising Suns</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>Coalition (Summer 2025)=2</t>
         </is>
       </c>
     </row>
@@ -23536,15 +23536,15 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Team Thetford</t>
+          <t>K-W Vipers</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NSC=1</t>
+          <t>Coalition (Summer 2025)=2</t>
         </is>
       </c>
     </row>
@@ -23554,15 +23554,15 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Top Left</t>
+          <t>Milton Stags</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NJC=1</t>
+          <t>Coalition (Summer 2025)=2</t>
         </is>
       </c>
     </row>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Triple Balance</t>
+          <t>506 Elite Jr Academy</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -23580,7 +23580,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NSC=1</t>
+          <t>NJC=1</t>
         </is>
       </c>
     </row>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>UEWB</t>
+          <t>Against The Six Prep</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -23608,7 +23608,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ridley College</t>
+          <t>C.O.D.E Academy</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>OSBA-coalition=1</t>
+          <t>NJC=1</t>
         </is>
       </c>
     </row>
@@ -23626,7 +23626,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cambridge International Academy</t>
+          <t>Canada Topflight Academy</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -23634,7 +23634,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>OSBA-coalition=1</t>
+          <t>NJC=1</t>
         </is>
       </c>
     </row>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>King's Christian Collegiate</t>
+          <t>CKATT</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -23652,7 +23652,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>OSBA-coalition=1</t>
+          <t>NJC=1</t>
         </is>
       </c>
     </row>
@@ -23662,7 +23662,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Redmond Basketball</t>
+          <t>Collective Elite Academy</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -23670,7 +23670,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>OSBA-coalition=1</t>
+          <t>NJC=1</t>
         </is>
       </c>
     </row>
@@ -23680,7 +23680,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Richmond Hill Ascend Prep</t>
+          <t>Cooksville We&gt;Me</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>OSBA-coalition=1</t>
+          <t>NJC=1</t>
         </is>
       </c>
     </row>
@@ -23698,7 +23698,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ace Acumen Heights</t>
+          <t>Dynamic Basketball</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -23706,7 +23706,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>OSBA-coalition=1</t>
+          <t>NSC=1</t>
         </is>
       </c>
     </row>
@@ -23716,7 +23716,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>AD Rebelles</t>
+          <t>Elton Academy</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>OSBA-coalition=1</t>
+          <t>NSC=1</t>
         </is>
       </c>
     </row>
@@ -23734,7 +23734,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Southwest Academy</t>
+          <t>F.O.R.M. Basketball Academy</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -23742,7 +23742,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>OSBA-coalition=1</t>
+          <t>NSC=1</t>
         </is>
       </c>
     </row>
@@ -23752,7 +23752,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>St. Michael's College</t>
+          <t>Gators Basketball Academy</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -23760,12 +23760,1578 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>OSBA-coalition=1</t>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>GBU</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Ignite Academy</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Kings Court Academy</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>M&amp;R Basketball</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>NSE Select Academy</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>RSB Elite</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>RWI519</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SCI Spartans</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Strive Hoops</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Team Sanctuary</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Team Thetford</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Top Left</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Triple Balance</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>UEWB</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>William Academy</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>AAA Academy</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Against the Six</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Alma Prep</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>B1CE London</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BALL905 Elite</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Barrie Buccaneers</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Blessed Sacrament</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Brantford Hawks</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Burlington Force</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Burlington Hoops Academy</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>C.O.D.E Sports Academy</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>WNPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>CB Elite</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CSJV Prep Basketball QC</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Canada Central Prep</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Canadian Private School</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Capital Courts</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Cathedral</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Crestwood Prep</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>DEl1te</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>DFA Academy</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Dundas Dynamo</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Durham Gators</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>École St-Gabriel Escadron</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Father Henry Carr</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>First Step Elite Gold</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Fitz Youth</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Fundamentals First</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>GT Elite</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>GYBA Gryphons</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Grassroots Niagara</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Gwillimbury Basketball United</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>HQ Elite</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Hamilton Elite</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>HoopHer</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Hooptrotters OGs</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>J. Addison Jaguars</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>K9 Elite White</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Lead2Greatness</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Mississauga Monarchs</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Momentum Basketball</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Norwood Stars</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Notre Dame Hounds SK</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>WNPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Oakville Panthers</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Oakville Vytis</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Orillia Lakers</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Ottawa Prospects</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Prolific Sports Academy</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Rothesay Netherwood School NB</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Sacred Heart Montreal</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>WNPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>TC Soldiers</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Team CB</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>The Conglomerate</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>1</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Thornhill Thunder</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Tornades Basketball</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Toronto Top Tier East</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Union Elite</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Victory Prep</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>West Ottawa</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>William Prep</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>1</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>YASO Basketball Academy Black</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Cambridge International Academy</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Redmond Basketball</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Richmond Hill Ascend Prep</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Ace Acumen Heights</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>AD Rebelles</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>St. Michael's College</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>North Toronto Huskies (NTBA)</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Etobicoke Thunder</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Barrie Royals</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Blessed Sacrament (Yellow Jackets)</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Toronto Triple Threat</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Silver Knights (SilverKnights Elite)</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D129"/>
+  <autoFilter ref="A1:D216"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/research/provinces/SportsHub-Ontario.xlsx
+++ b/docs/research/provinces/SportsHub-Ontario.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Club-League Map" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Club Sizes (ON)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Club Sizes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$188</definedName>
@@ -19,6 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$264</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$142</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Club Sizes (ON)'!$A$1:$D$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Club Sizes'!$A$1:$C$216</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25334,4 +25336,3266 @@
   <autoFilter ref="A1:D216"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C216"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Teams counted (directional)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Breakdown (league=teams)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Scarborough Blues / SBA (Team {coach}, Premier)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=18</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>The MUMBA Mentality</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>YvY</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Toronto Lords</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=7; NPH-SL=2; NSC=1; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Eurostep</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Burloak</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dragons de Gatineau</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NPH-SL=8; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Brampton Warriors</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>iDream by BOA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Born 2 Stand Out</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Royal Crown</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NPH-SL=3; NPH-D1=3; NPA=1; WNPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Durham Blues</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Wiggins Elite</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NPH-SL=4; NJC=2; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>City Above</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Hoopzone Knights</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FEIA (Fort Erie)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NPH-D1=3; NPH-SL=1; NPA=1; WNPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ottawa Elite (incl. Prep)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NPH-SL=4; NPH-D1=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>St. Jude's Prep/Academy</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NPH-D1=4; NPA=1; WNPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Lincoln Prep</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>OSBA=4; NPH-D1=1; NPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C.O.D.E. Academy (Provincial + International)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OSBA=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Future Hope Academy</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>OSBA=3; NJC=1; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Monarchs</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=4; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PDM Basketball</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NPH-SL=4; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>St. Jude's Academy (Blue + White in Trillium)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>OSBA=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Brampton City Prep (Nat/Prov + Reg/North + South)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>OSBA=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>YNBA (incl. Avengers)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>City Above Elite</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NPH-SL=3; NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ONL-X</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1; NPH-SL=1; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Simcoe United</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NJC=2; NSC=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Burloak Elite</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NPH-SL=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CE23 Academy</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NPH-SL=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NPH-SL=2; NPH-D1=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NDL</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NPH-SL=3; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>North York Lions</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NPH-SL=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RWI</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NPH-SL=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Underdog Elite</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NPH-SL=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Tall Pines Academy</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NPH-SL=2; NPH-D1=1; OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Royal Crown School</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OSBA=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Crestwood Prep (incl. Blue in W)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>OSBA=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Orangeville Prep / Athlete Institute</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OSBA=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Victory Academy / Victory Prep (East + West)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>OSBA=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>East York Eagles</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Brampton City Prep</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NJC=2; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Brotherhood Elite</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NPH-SL=2; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Full Circle Basketball Academy</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1; OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>G2S Game Changers</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>NPH-SL=2; NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SC Academy Prep</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NSC=2; NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SSF Blizzard</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NJC=2; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Tri-City Prep</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OSBA=2; NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Tru Balance</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>NPH-SL=2; NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Vanguard (North)</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NSC=2; NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CKATT Basketball</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>NPH-SL=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Dropoff Elite</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NPH-SL=2; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Edge School (Calgary)</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NPH-D1=1; NPA=1; WNPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>M and R Basketball</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NPH-SL=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MC Elite</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>NPH-SL=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Polaris Prep</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>NPH-D1=2; NPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SC Academy</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>NPH-SL=2; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Simcoe United Spartans</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>NPH-SL=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TNP</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>NPH-SL=2; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Tri-City (Prep/Academy)</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>NPH-D1=2; NPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Vanguard North Prep</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>NPH-SL=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Westfield Secondary</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NPH-D1=2; NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Vaughan Panthers</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>NPH-SL=2; Coalition (Summer 2025)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>James Cardinal McGuigan</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OSBA=2; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Niagara Prep</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>OSBA=2; WNPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Uchenna Academy</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>OSBA=2; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Fort Erie International Academy</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>OSBA=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Hodan Prep (incl. Nighthawks)</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OSBA=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>William Academy (incl. Cobourg)</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>OSBA=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Canada Topflight Academy (Gold + Red)</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>OSBA=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Polaris Prep Academy (Gold + Black)</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>OSBA=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>King Heights Academy</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>OSBA=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Colts Prep</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>OSBA=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Father Henry Carr (Jr. Prep + Freshmen Prep)</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>3</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>OSBA=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Alpha Elite</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>NJC=1; NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Cali Prep</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Compass Academy</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Eastern Basketball Academy</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>NJC=1; NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>HQ Prep</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>NJC=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Jungle Prep</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>LBA</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>London Ramblers</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>NJC=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Orangeville Prep</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>2</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>NSC=1; NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Project Excellence</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SBA Premier</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Ste Cecile Academy</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NSC=1; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Top Notch Prep</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>NJC=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Westfield Prep</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>2</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Wolverines Elite</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NJC=1; NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>BCP</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>2</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>NPH-D1=1; NPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Dynastie</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>NPH-D1=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>EM Elite</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>NPH-SL=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Eurostep Basketball</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>NPH-SL=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Hamilton Transformation Academy</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NPH-SL=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Hodan Prep</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>NPH-D1=1; NPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>King Heights</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>NPH-SL=1; NPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Kings Court Basketball</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NPH-SL=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Malton Sting Basketball</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>2</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>NPH-SL=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>North Toronto Huskies</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>2</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>NPH-SL=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Retro Elite</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>NPH-SL=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>St. Michael's College School</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>NPH-SL=1; NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Waterloo Wolverines Elite</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>NPH-SL=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>West United Prep</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>NPH-SL=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>YvY Elite</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>2</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>NPH-SL=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>King's Christian Collegiate</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>2</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>WNPA=1; OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ridley College</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>NPA=1; OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Southwest Academy</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>NPH-D1=1; OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Inspire Academy</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>2</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>OSBA=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Lo-Ellen Park Prep</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>2</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>OSBA=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>J.Addison School</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>2</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>OSBA=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Capital Courts Academy</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>2</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>OSBA=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Louis-Riel (Academy)</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>2</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>OSBA=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>H5 Academy</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>2</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>OSBA=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Durham Rising Suns</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>2</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>K-W Vipers</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Milton Stags</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>2</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>506 Elite Jr Academy</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Against The Six Prep</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>C.O.D.E Academy</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Canada Topflight Academy</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CKATT</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Collective Elite Academy</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Cooksville We&gt;Me</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Dynamic Basketball</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Elton Academy</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>F.O.R.M. Basketball Academy</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Gators Basketball Academy</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>GBU</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Ignite Academy</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Kings Court Academy</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>M&amp;R Basketball</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>NSE Select Academy</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>RSB Elite</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>RWI519</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SCI Spartans</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Strive Hoops</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Team Sanctuary</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Team Thetford</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Top Left</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Triple Balance</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>NSC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>UEWB</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>William Academy</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>NJC=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>AAA Academy</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Against the Six</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Alma Prep</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>B1CE London</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>BALL905 Elite</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Barrie Buccaneers</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Blessed Sacrament</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Brantford Hawks</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Burlington Force</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Burlington Hoops Academy</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>C.O.D.E Sports Academy</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>WNPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CB Elite</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CSJV Prep Basketball QC</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>NPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Canada Central Prep</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Canadian Private School</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Capital Courts</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Cathedral</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Crestwood Prep</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>NPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>DEl1te</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>DFA Academy</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Dundas Dynamo</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Durham Gators</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>École St-Gabriel Escadron</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Father Henry Carr</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>First Step Elite Gold</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Fitz Youth</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Fundamentals First</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>GT Elite</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>GYBA Gryphons</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Grassroots Niagara</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Gwillimbury Basketball United</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>HQ Elite</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Hamilton Elite</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>HoopHer</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Hooptrotters OGs</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>1</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>J. Addison Jaguars</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>K9 Elite White</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Lead2Greatness</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Mississauga Monarchs</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Momentum Basketball</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Norwood Stars</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Notre Dame Hounds SK</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>WNPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Oakville Panthers</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Oakville Vytis</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>1</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Orillia Lakers</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Ottawa Prospects</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Prolific Sports Academy</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Rothesay Netherwood School NB</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>NPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Sacred Heart Montreal</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>WNPA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>TC Soldiers</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Team CB</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>The Conglomerate</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>1</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Thornhill Thunder</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Tornades Basketball</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Toronto Top Tier East</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Union Elite</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Victory Prep</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>West Ottawa</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>William Prep</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>NPH-D1=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>YASO Basketball Academy Black</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>NPH-SL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Cambridge International Academy</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Redmond Basketball</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Richmond Hill Ascend Prep</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Ace Acumen Heights</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>AD Rebelles</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>St. Michael's College</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>OSBA=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>North Toronto Huskies (NTBA)</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Etobicoke Thunder</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Barrie Royals</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Blessed Sacrament (Yellow Jackets)</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Toronto Triple Threat</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Silver Knights (SilverKnights Elite)</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Coalition (Summer 2025)=1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C216"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/research/provinces/SportsHub-Ontario.xlsx
+++ b/docs/research/provinces/SportsHub-Ontario.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Club Sizes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$Q$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$264</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$142</definedName>
@@ -67,11 +67,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P188"/>
+  <dimension ref="A1:Q188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -456,6 +457,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -539,6 +541,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -643,6 +650,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -772,6 +782,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -980,6 +993,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1141,6 +1157,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1208,6 +1227,9 @@
           <t>Multi-division</t>
         </is>
       </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1354,6 +1376,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1468,6 +1493,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1619,6 +1647,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1857,6 +1888,9 @@
           <t>NPA Champions</t>
         </is>
       </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2184,6 +2218,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2246,6 +2283,9 @@
           <t>Multi-league</t>
         </is>
       </c>
+      <c r="Q32" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2489,6 +2529,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q36" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2729,6 +2772,9 @@
           <t>Women's</t>
         </is>
       </c>
+      <c r="Q41" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2858,6 +2904,9 @@
           <t>Multi-league</t>
         </is>
       </c>
+      <c r="Q43" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2925,6 +2974,9 @@
           <t>North American exposure tournaments</t>
         </is>
       </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3359,6 +3411,9 @@
           <t>Coached by Carl English</t>
         </is>
       </c>
+      <c r="Q51" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3416,6 +3471,9 @@
           <t>Grade 8</t>
         </is>
       </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3473,6 +3531,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q53" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3602,6 +3663,9 @@
           <t>U15 to U19</t>
         </is>
       </c>
+      <c r="Q55" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3664,6 +3728,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3788,6 +3855,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3951,6 +4021,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3988,6 +4061,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q63" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4109,6 +4185,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4171,6 +4250,9 @@
           <t>Grade 9</t>
         </is>
       </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4265,6 +4347,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4401,6 +4486,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q72" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4574,6 +4662,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4685,6 +4776,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q79" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4747,6 +4841,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q80" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5029,6 +5126,9 @@
           <t>U15 to U19</t>
         </is>
       </c>
+      <c r="Q86" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5170,6 +5270,9 @@
           <t>Gold team</t>
         </is>
       </c>
+      <c r="Q89" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5217,6 +5320,9 @@
           <t>Grade 9-10</t>
         </is>
       </c>
+      <c r="Q90" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5254,6 +5360,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q91" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5400,6 +5509,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q94" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5452,6 +5564,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q95" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5670,6 +5785,9 @@
           <t>White team</t>
         </is>
       </c>
+      <c r="Q99" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5769,6 +5887,9 @@
           <t>New NPA entrant</t>
         </is>
       </c>
+      <c r="Q101" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5806,6 +5927,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q102" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5843,6 +5967,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q103" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5905,6 +6032,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q104" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6009,6 +6139,9 @@
           <t>Grade 10 and Grade 12 divisions</t>
         </is>
       </c>
+      <c r="Q106" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6071,6 +6204,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q107" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6192,6 +6328,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q110" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6343,6 +6482,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q113" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6405,6 +6547,9 @@
           <t>International roster</t>
         </is>
       </c>
+      <c r="Q114" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6457,6 +6602,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6603,6 +6751,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q118" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6702,6 +6853,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q120" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6863,6 +7017,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6920,6 +7077,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7029,6 +7189,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7066,6 +7229,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7103,6 +7269,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7239,6 +7408,9 @@
           <t>U13 to U19</t>
         </is>
       </c>
+      <c r="Q131" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7328,6 +7500,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q133" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7417,6 +7592,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q135" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7464,6 +7642,9 @@
           <t>Grade 10-12</t>
         </is>
       </c>
+      <c r="Q136" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7637,6 +7818,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q140" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7875,6 +8059,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q144" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8165,6 +8352,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q149" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8212,6 +8402,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q150" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8440,6 +8633,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8611,6 +8807,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q157" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8673,6 +8872,9 @@
           <t>Multi-league</t>
         </is>
       </c>
+      <c r="Q158" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8938,6 +9140,9 @@
           <t>Multi-league</t>
         </is>
       </c>
+      <c r="Q163" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9124,6 +9329,9 @@
           <t>Multi-league powerhouse</t>
         </is>
       </c>
+      <c r="Q166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9424,6 +9632,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q171" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9543,6 +9754,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9605,6 +9819,9 @@
           <t>Inner-city focus since 2003</t>
         </is>
       </c>
+      <c r="Q174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10029,6 +10246,9 @@
           <t>ontario census + enrichment 2026-07-18</t>
         </is>
       </c>
+      <c r="Q181" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10210,6 +10430,9 @@
           <t>Gold and Black teams</t>
         </is>
       </c>
+      <c r="Q184" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10415,7 +10638,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P188"/>
+  <autoFilter ref="A1:Q188"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
